--- a/data/output/20260922/pureComponents_filled.xlsx
+++ b/data/output/20260922/pureComponents_filled.xlsx
@@ -491,18 +491,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>229.5953381943012</v>
+        <v>226.3892895068535</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>8.224442329737116</v>
+        <v>8.092697027255742</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>31.03326116171689</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -519,18 +517,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>379.5446995964523</v>
+        <v>450.3011832115711</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>15.57360675408547</v>
+        <v>-191.4365340526395</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>-167.9397827707267</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
     </row>
@@ -547,18 +543,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>263.991599735307</v>
+        <v>251.8661107120695</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>11.01308011583512</v>
+        <v>10.53118778433254</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>127.9753986368301</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
     </row>
@@ -575,18 +569,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>376.9903242147047</v>
+        <v>423.4580742726941</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>15.43546081846497</v>
+        <v>160.2567452866502</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>-161.9414109883178</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
     </row>
@@ -603,18 +595,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>220.4952927356041</v>
+        <v>227.4809965371188</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>8.612858277832489</v>
+        <v>10.03470583257606</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>-18.6576752533642</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
     </row>
@@ -631,18 +621,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>390.6155567399203</v>
+        <v>499.9677229649849</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>16.2221298172677</v>
+        <v>-52.91311373437054</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>-190.8226227764988</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
     </row>
@@ -659,18 +647,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>400.0104167888355</v>
+        <v>522.2579954860856</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>16.83933778061437</v>
+        <v>49.39676426026924</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>-212.4125235501348</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
     </row>
@@ -687,18 +673,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>385.4283221427298</v>
+        <v>356.432002110875</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>15.93020990275853</v>
+        <v>19.73137960112631</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>-181.7980480891555</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
     </row>
@@ -715,18 +699,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>399.0226241977145</v>
+        <v>703.434473107194</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>16.80489386552829</v>
+        <v>33.137248280394</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>-211.7668389432339</v>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
     </row>
@@ -743,18 +725,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>243.3817283959062</v>
+        <v>245.7987390237712</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>8.041160184610801</v>
+        <v>8.14003638974062</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>252.2137470823162</v>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
     </row>
@@ -771,18 +751,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>336.3178714354951</v>
+        <v>389.2439188910884</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>12.88933665528702</v>
+        <v>79.15850037556592</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
-        <v>-59.79462134513255</v>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
     </row>
@@ -799,18 +777,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>390.4088502825291</v>
+        <v>385.4352795512679</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>16.23697928581094</v>
+        <v>42.75012945138688</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>-193.1519834717552</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
     </row>
@@ -827,18 +803,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>174.487852164023</v>
+        <v>187.2667656788124</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>5.831168407214987</v>
+        <v>6.207543249236824</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>21.24515525454319</v>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
     </row>
@@ -855,18 +829,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>200.1203870785064</v>
+        <v>234.7663288068059</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>9.317761872511518</v>
+        <v>10.91574654358259</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>-3.37162634082523</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
     </row>
@@ -883,18 +855,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>347.6146274400004</v>
+        <v>348.4115254173495</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>13.73338705547436</v>
+        <v>35.96317781896198</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>-82.94982236098593</v>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
     </row>
@@ -911,18 +881,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>376.8411750655586</v>
+        <v>310.1181829155213</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>15.56438031318553</v>
+        <v>18.83509438849234</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>-177.7882204599887</v>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -939,18 +907,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>341.8136898197265</v>
+        <v>406.5756940760526</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>13.39443373107565</v>
+        <v>128.9856813544949</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>-67.78166587199587</v>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
     </row>
@@ -967,18 +933,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>189.0839614276538</v>
+        <v>319.9699338330606</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>5.592015211172276</v>
+        <v>18.4333348524455</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>-16.42620622595456</v>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
     </row>
@@ -995,18 +959,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>261.855890325781</v>
+        <v>326.4810764010267</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>9.186315666105367</v>
+        <v>25.02976008472713</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>-97.32000608128834</v>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
     </row>
@@ -1023,18 +985,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>140.4802932397637</v>
+        <v>158.4976684731346</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>4.641482828025653</v>
+        <v>5.207380181768777</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>-115.0635873726757</v>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
     </row>
@@ -1051,18 +1011,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>274.1853729698994</v>
+        <v>342.2077960428663</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>10.56297791002852</v>
+        <v>35.10419647335656</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="n">
-        <v>-45.0095252188278</v>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
     </row>
@@ -1079,18 +1037,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>343.9315711447974</v>
+        <v>387.2269891417278</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>13.31162076641347</v>
+        <v>63.52825053077514</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
-        <v>-101.1809829525155</v>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
     </row>
@@ -1107,18 +1063,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>375.0947326930199</v>
+        <v>582.9843277030036</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>15.33067475693588</v>
+        <v>-19.31319426951159</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
-        <v>-155.4061483905829</v>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
     </row>
@@ -1135,18 +1089,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>879.7149078635194</v>
+        <v>918.5868607059249</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>19.89749282495182</v>
+        <v>20.65972133376436</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="n">
-        <v>-387.3872674249705</v>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
     </row>
@@ -1163,18 +1115,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>373.532499167082</v>
+        <v>381.3172928364659</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>15.43252244907036</v>
+        <v>27.14027069905195</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>-187.9700019344332</v>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
     </row>
@@ -1191,18 +1141,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>184.3227502679831</v>
+        <v>171.0398804679537</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>6.137264946575097</v>
+        <v>5.71422486370682</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>-63.07957388031329</v>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
     </row>
@@ -1219,18 +1167,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>181.5409294150604</v>
+        <v>209.9915721786144</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>6.550600485755194</v>
+        <v>7.57787209793128</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>-99.22598503181422</v>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
     </row>
@@ -1247,18 +1193,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>212.0947417956594</v>
+        <v>346.7683839583349</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>9.317597209427909</v>
+        <v>39.3888421190459</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
-        <v>-22.7958176238468</v>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
     </row>
@@ -1275,18 +1219,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>184.4545026921743</v>
+        <v>197.9081943516057</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>6.284085485103493</v>
+        <v>6.70523962523245</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>-18.22463148641029</v>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
     </row>
@@ -1303,18 +1245,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>220.9072683584693</v>
+        <v>349.765465914536</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>10.35947947147404</v>
+        <v>29.32556113545014</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
-        <v>-12.6144540708427</v>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
     </row>
@@ -1331,18 +1271,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>389.811233576756</v>
+        <v>501.7924243507575</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>16.17190199772164</v>
+        <v>-63.4674126522944</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>-188.8113694151429</v>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
     </row>
@@ -1359,18 +1297,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1032.890144478551</v>
+        <v>991.5371623508091</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>26.07305047857039</v>
+        <v>25.37172393918426</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="n">
-        <v>-420.2077568810129</v>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
     </row>
@@ -1387,18 +1323,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>421.0939305080225</v>
+        <v>525.1242213110955</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>17.98121578967652</v>
+        <v>53.14280116447933</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
-        <v>-222.0301171077888</v>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
     </row>
@@ -1415,18 +1349,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>179.4586182008552</v>
+        <v>193.6613801406016</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>5.019351672291954</v>
+        <v>5.440667333186951</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>17.31890548389035</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
     </row>
@@ -1443,18 +1375,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>196.5324713370753</v>
+        <v>218.0337498063079</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>11.20440561927183</v>
+        <v>12.27906347435003</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>-113.8552414677842</v>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
     </row>
@@ -1471,18 +1401,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>411.6515683250204</v>
+        <v>775.8756503773725</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>17.05984350534146</v>
+        <v>29.40796543745662</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>-219.0548789188128</v>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
     </row>
@@ -1499,18 +1427,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>379.704202946192</v>
+        <v>505.7480549392224</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>15.56921869956924</v>
+        <v>-42.48405209319603</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
-        <v>-164.8693203778666</v>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
     </row>
@@ -1527,18 +1453,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1055.167398476056</v>
+        <v>920.8646092397905</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>29.91364357419237</v>
+        <v>26.68192273838175</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
-        <v>-419.6510469450723</v>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
     </row>
@@ -1555,18 +1479,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>419.5142968233575</v>
+        <v>518.6883891234099</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>17.88982452834415</v>
+        <v>47.50047023522843</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
-        <v>-220.6332179081222</v>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
     </row>
@@ -1583,18 +1505,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>399.3752271883509</v>
+        <v>414.1752514795634</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>14.07459323085117</v>
+        <v>14.59561515971462</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="n">
-        <v>-458.4332178958391</v>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
     </row>
@@ -1611,18 +1531,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>336.3956111669228</v>
+        <v>409.3940432217667</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>20.43864894943134</v>
+        <v>24.6081729776041</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="n">
-        <v>-505.270689589023</v>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
     </row>
@@ -1639,18 +1557,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>425.9010020885216</v>
+        <v>469.487295515833</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>9.789287612143475</v>
+        <v>11.01407567445179</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
-        <v>-443.5699511715027</v>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
     </row>
@@ -1667,18 +1583,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>398.6773342514541</v>
+        <v>446.5707495750706</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>15.28325926369379</v>
+        <v>16.98422981645019</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="n">
-        <v>-553.7157057469428</v>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
     </row>
@@ -1695,18 +1609,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>398.8772161307521</v>
+        <v>445.2457014155436</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>16.80201448235014</v>
+        <v>28.0399530896236</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="n">
-        <v>-211.6827037221836</v>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
     </row>
@@ -1723,18 +1635,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>529.5101058984635</v>
+        <v>524.8662166871308</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>16.76060648338538</v>
+        <v>16.74382374937468</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="n">
-        <v>-385.6435577254006</v>
-      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
     </row>
@@ -1751,18 +1661,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>526.7783277539697</v>
+        <v>497.8406231404214</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>50.83539178504013</v>
+        <v>48.20352735502853</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="n">
-        <v>-414.2258222703319</v>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
     </row>
@@ -1779,18 +1687,16 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>428.3562484124578</v>
+        <v>465.2481638931996</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>13.43688257405838</v>
+        <v>27.60975355685752</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="n">
-        <v>-326.2922193362025</v>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
     </row>
@@ -1807,18 +1713,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>481.994278882019</v>
+        <v>528.3450591688693</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>24.22769383340556</v>
+        <v>26.94180774226215</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="n">
-        <v>-422.2500425167066</v>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
     </row>
@@ -1835,18 +1739,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>398.5280440067932</v>
+        <v>408.7690753608349</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>15.59807525498589</v>
+        <v>17.67838115849661</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="n">
-        <v>-198.4228729733461</v>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
     </row>
@@ -1863,18 +1765,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>373.8619563931495</v>
+        <v>370.8687945277871</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>13.77131763010763</v>
+        <v>13.92327352169858</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="n">
-        <v>-190.7714065039811</v>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
     </row>
@@ -1891,18 +1791,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>421.1884524310292</v>
+        <v>469.6567218693743</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>16.43407807195475</v>
+        <v>29.39428131939636</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
-        <v>-261.4587835937899</v>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
     </row>
@@ -1919,18 +1817,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>633.2317000484289</v>
+        <v>665.9568476071037</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>20.31528553381087</v>
+        <v>21.71347510611127</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="n">
-        <v>-271.9814121506617</v>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
     </row>
@@ -1947,18 +1843,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>379.7622802674297</v>
+        <v>460.055267910623</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>12.34613134206438</v>
+        <v>36.01194381785113</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="n">
-        <v>-210.7479999173271</v>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
     </row>
@@ -1975,18 +1869,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>670.7154694721073</v>
+        <v>595.7530177906182</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>36.57221655076368</v>
+        <v>33.00591659125514</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="n">
-        <v>-349.464252941762</v>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
     </row>
@@ -2003,18 +1895,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>376.8368549789185</v>
+        <v>380.0230060656417</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>40.8104536603456</v>
+        <v>40.66645921771299</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="n">
-        <v>-540.8836658140318</v>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
     </row>
@@ -2031,18 +1921,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>298.3636545366557</v>
+        <v>698.3088112934618</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>1.321230276495479</v>
+        <v>3.321720839474093</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="n">
-        <v>-56.83828365329745</v>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
     </row>
@@ -2059,18 +1947,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>411.2116717593236</v>
+        <v>402.0641178859806</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>39.22671718901023</v>
+        <v>38.19918785447543</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="n">
-        <v>-515.8357950381383</v>
-      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
     </row>
@@ -2087,18 +1973,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>609.3391627562414</v>
+        <v>595.1090445991102</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>7.661606577004836</v>
+        <v>7.685670527933858</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="n">
-        <v>-397.7194684701461</v>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
     </row>
@@ -2115,18 +1999,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>469.9409997944014</v>
+        <v>445.682160448657</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>66.00615527025792</v>
+        <v>62.34772317260103</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="n">
-        <v>-530.6308827016483</v>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
     </row>
@@ -2143,18 +2025,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>439.1873504276282</v>
+        <v>467.04608389043</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>13.45416981455587</v>
+        <v>18.6784586277804</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="n">
-        <v>-380.9913977015016</v>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
     </row>
@@ -2171,18 +2051,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>175.9204747815729</v>
+        <v>159.9355861003573</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>7.514011255335669</v>
+        <v>6.81494083153923</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="n">
-        <v>8.40774020895293</v>
-      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
     </row>
@@ -2199,18 +2077,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>563.9079335932121</v>
+        <v>714.6626690710948</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>7.215055893917345</v>
+        <v>8.928829899198931</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="n">
-        <v>-178.3964633243076</v>
-      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
     </row>
@@ -2227,18 +2103,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>398.868821448906</v>
+        <v>297.390542360336</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>16.79884899706422</v>
+        <v>11.14460220566998</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="n">
-        <v>-211.6660712525518</v>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
     </row>
@@ -2255,18 +2129,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>360.2522836744195</v>
+        <v>156.3528385658726</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>14.074105308135</v>
+        <v>3.641431840967785</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="n">
-        <v>-143.0925882261594</v>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
     </row>
@@ -2283,18 +2155,16 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>359.2315148070163</v>
+        <v>327.5028095393986</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>14.34206414403562</v>
+        <v>22.53846015202668</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="n">
-        <v>-153.4460711169909</v>
-      </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
     </row>
@@ -2311,18 +2181,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>294.5697427648989</v>
+        <v>294.0240022906991</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>12.40779116701745</v>
+        <v>16.04133371754528</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="n">
-        <v>-122.0102904136775</v>
-      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
     </row>

--- a/data/output/20260922/pureComponents_filled.xlsx
+++ b/data/output/20260922/pureComponents_filled.xlsx
@@ -491,12 +491,12 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>226.3892895068535</v>
+        <v>230.5285601407318</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>8.092697027255742</v>
+        <v>8.218579856978019</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -517,12 +517,12 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>450.3011832115711</v>
+        <v>280.6272773554851</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>-191.4365340526395</v>
+        <v>5.324332267600289</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -543,12 +543,12 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>251.8661107120695</v>
+        <v>258.0220272860158</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>10.53118778433254</v>
+        <v>10.86072117746967</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -569,12 +569,12 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>423.4580742726941</v>
+        <v>289.5485006821258</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>160.2567452866502</v>
+        <v>12.86724069769583</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -595,12 +595,12 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>227.4809965371188</v>
+        <v>217.721040797028</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>10.03470583257606</v>
+        <v>9.201250578834143</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -621,12 +621,12 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>499.9677229649849</v>
+        <v>298.9230725109284</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>-52.91311373437054</v>
+        <v>12.00235307737671</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -647,12 +647,12 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>522.2579954860856</v>
+        <v>620.5705802601036</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>49.39676426026924</v>
+        <v>24.50898429830133</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -673,12 +673,12 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>356.432002110875</v>
+        <v>310.5351298771114</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>19.73137960112631</v>
+        <v>10.53613642935987</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -699,12 +699,12 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>703.434473107194</v>
+        <v>813.4528537523943</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>33.137248280394</v>
+        <v>25.63856825377426</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -725,12 +725,12 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>245.7987390237712</v>
+        <v>243.4865039945783</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>8.14003638974062</v>
+        <v>8.078937119136503</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -751,12 +751,12 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>389.2439188910884</v>
+        <v>171.831594423355</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>79.15850037556592</v>
+        <v>6.708681385557764</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -777,12 +777,12 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>385.4352795512679</v>
+        <v>260.614629597831</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>42.75012945138688</v>
+        <v>9.147753496969308</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -803,12 +803,12 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>187.2667656788124</v>
+        <v>181.2294101301109</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>6.207543249236824</v>
+        <v>6.00215753929527</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -829,12 +829,12 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>234.7663288068059</v>
+        <v>224.4681653878412</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>10.91574654358259</v>
+        <v>10.32400807911261</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -855,12 +855,12 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>348.4115254173495</v>
+        <v>119.8921695248892</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>35.96317781896198</v>
+        <v>3.618684123501609</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -881,12 +881,12 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>310.1181829155213</v>
+        <v>283.1115522992301</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>18.83509438849234</v>
+        <v>14.30054841045704</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -907,12 +907,12 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>406.5756940760526</v>
+        <v>147.4891082691907</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>128.9856813544949</v>
+        <v>5.701811343694116</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -933,12 +933,12 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>319.9699338330606</v>
+        <v>223.1330853050393</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>18.4333348524455</v>
+        <v>7.084764141270908</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -959,12 +959,12 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>326.4810764010267</v>
+        <v>204.682921829022</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>25.02976008472713</v>
+        <v>7.547390227858426</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -985,12 +985,12 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>158.4976684731346</v>
+        <v>146.0176258382641</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>5.207380181768777</v>
+        <v>4.745191002580068</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1011,12 +1011,12 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>342.2077960428663</v>
+        <v>206.3317690555035</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>35.10419647335656</v>
+        <v>8.810765928619837</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1037,12 +1037,12 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>387.2269891417278</v>
+        <v>219.9356143716117</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>63.52825053077514</v>
+        <v>8.904997046417753</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1063,12 +1063,12 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>582.9843277030036</v>
+        <v>324.8858149551142</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>-19.31319426951159</v>
+        <v>12.29757140675225</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1089,12 +1089,12 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>918.5868607059249</v>
+        <v>897.3503321782962</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>20.65972133376436</v>
+        <v>20.10986367569337</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1115,12 +1115,12 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>381.3172928364659</v>
+        <v>327.8699504493716</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>27.14027069905195</v>
+        <v>11.77031869105104</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1141,12 +1141,12 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>171.0398804679537</v>
+        <v>175.9936288449216</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>5.71422486370682</v>
+        <v>5.897597573930398</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1167,12 +1167,12 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>209.9915721786144</v>
+        <v>186.8977944487656</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>7.57787209793128</v>
+        <v>6.646747532657145</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1193,12 +1193,12 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>346.7683839583349</v>
+        <v>159.8358667878036</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>39.3888421190459</v>
+        <v>6.005338938476806</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1219,12 +1219,12 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>197.9081943516057</v>
+        <v>190.7199357722525</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>6.70523962523245</v>
+        <v>6.404152470348823</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1245,12 +1245,12 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>349.765465914536</v>
+        <v>271.821000306116</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>29.32556113545014</v>
+        <v>12.18657463626084</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1271,12 +1271,12 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>501.7924243507575</v>
+        <v>265.8211763515511</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>-63.4674126522944</v>
+        <v>10.74379049118423</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1297,12 +1297,12 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>991.5371623508091</v>
+        <v>973.4971391132553</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>25.37172393918426</v>
+        <v>25.7796215783605</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1323,12 +1323,12 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>525.1242213110955</v>
+        <v>652.8253975553612</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>53.14280116447933</v>
+        <v>24.20512501055465</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1349,12 +1349,12 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>193.6613801406016</v>
+        <v>178.0462564070317</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>5.440667333186951</v>
+        <v>5.002051537283394</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1375,12 +1375,12 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>218.0337498063079</v>
+        <v>210.4835487112126</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>12.27906347435003</v>
+        <v>11.62954266891588</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1401,12 +1401,12 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>775.8756503773725</v>
+        <v>836.9657162841271</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>29.40796543745662</v>
+        <v>25.55801144591133</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1427,12 +1427,12 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>505.7480549392224</v>
+        <v>314.3849130027971</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>-42.48405209319603</v>
+        <v>12.36220784399122</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -1453,12 +1453,12 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>920.8646092397905</v>
+        <v>941.3822368859518</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>26.68192273838175</v>
+        <v>29.16181180896738</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -1479,12 +1479,12 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>518.6883891234099</v>
+        <v>605.6533090260397</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>47.50047023522843</v>
+        <v>23.93689418370924</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1505,12 +1505,12 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>414.1752514795634</v>
+        <v>400.0698603080006</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>14.59561515971462</v>
+        <v>14.04336509926725</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1531,12 +1531,12 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>409.3940432217667</v>
+        <v>369.3261914635831</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>24.6081729776041</v>
+        <v>21.38215395923003</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1557,12 +1557,12 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>469.487295515833</v>
+        <v>408.9187171577294</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>11.01407567445179</v>
+        <v>9.661157139776011</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1583,12 +1583,12 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>446.5707495750706</v>
+        <v>416.030095408967</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>16.98422981645019</v>
+        <v>15.53112752357966</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -1609,12 +1609,12 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>445.2457014155436</v>
+        <v>445.0421429510677</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>28.0399530896236</v>
+        <v>23.16235723016841</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -1635,12 +1635,12 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>524.8662166871308</v>
+        <v>519.1051742680455</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>16.74382374937468</v>
+        <v>16.80093378793335</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -1661,12 +1661,12 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>497.8406231404214</v>
+        <v>517.7394884356055</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>48.20352735502853</v>
+        <v>50.49074828756897</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1687,12 +1687,12 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>465.2481638931996</v>
+        <v>463.344199893606</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>27.60975355685752</v>
+        <v>20.2264858518564</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -1713,12 +1713,12 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>528.3450591688693</v>
+        <v>528.0177733738508</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>26.94180774226215</v>
+        <v>26.07672395943744</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>408.7690753608349</v>
+        <v>413.2245276675304</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>17.67838115849661</v>
+        <v>21.63457587142056</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -1765,12 +1765,12 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>370.8687945277871</v>
+        <v>358.0023127067872</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>13.92327352169858</v>
+        <v>13.61056997989314</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -1791,12 +1791,12 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>469.6567218693743</v>
+        <v>477.1484229395755</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>29.39428131939636</v>
+        <v>20.89166744696251</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -1817,12 +1817,12 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>665.9568476071037</v>
+        <v>618.0666352710888</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>21.71347510611127</v>
+        <v>20.3305892935719</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -1843,12 +1843,12 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>460.055267910623</v>
+        <v>467.7463813675583</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>36.01194381785113</v>
+        <v>21.55256924431178</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -1869,12 +1869,12 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>595.7530177906182</v>
+        <v>621.8777712385762</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>33.00591659125514</v>
+        <v>35.72453721443676</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -1895,12 +1895,12 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>380.0230060656417</v>
+        <v>392.4227631630488</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>40.66645921771299</v>
+        <v>41.37381407968098</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -1921,12 +1921,12 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>698.3088112934618</v>
+        <v>301.6057056798974</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>3.321720839474093</v>
+        <v>1.509591229103531</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -1947,12 +1947,12 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>402.0641178859806</v>
+        <v>415.892844833454</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>38.19918785447543</v>
+        <v>39.29695603483751</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -1973,12 +1973,12 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>595.1090445991102</v>
+        <v>530.3995707222064</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>7.685670527933858</v>
+        <v>7.17385580142242</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -1999,12 +1999,12 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>445.682160448657</v>
+        <v>471.5072030269084</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>62.34772317260103</v>
+        <v>65.98825674812392</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -2025,12 +2025,12 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>467.04608389043</v>
+        <v>445.732298841306</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>18.6784586277804</v>
+        <v>16.30911515392334</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -2051,12 +2051,12 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>159.9355861003573</v>
+        <v>157.8551200934199</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>6.81494083153923</v>
+        <v>6.685480711033231</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -2077,12 +2077,12 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>714.6626690710948</v>
+        <v>647.3257466924889</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>8.928829899198931</v>
+        <v>7.688863518536179</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -2103,12 +2103,12 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>297.390542360336</v>
+        <v>329.4695477701716</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>11.14460220566998</v>
+        <v>14.4621613489244</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -2129,12 +2129,12 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>156.3528385658726</v>
+        <v>285.9194523508135</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>3.641431840967785</v>
+        <v>11.89370044882708</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -2155,12 +2155,12 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>327.5028095393986</v>
+        <v>295.3629391829428</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>22.53846015202668</v>
+        <v>15.34660815434614</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -2181,12 +2181,12 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>294.0240022906991</v>
+        <v>280.7546698520774</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>16.04133371754528</v>
+        <v>13.64687074319993</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>

--- a/data/output/20260922/pureComponents_filled.xlsx
+++ b/data/output/20260922/pureComponents_filled.xlsx
@@ -491,12 +491,12 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>230.5285601407318</v>
+        <v>258.7313393292955</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>8.218579856978019</v>
+        <v>9.382535050020962</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -517,12 +517,12 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>280.6272773554851</v>
+        <v>-158.8591520830372</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>5.324332267600289</v>
+        <v>-0.7592581931408446</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -543,12 +543,12 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>258.0220272860158</v>
+        <v>250.0881919563437</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>10.86072117746967</v>
+        <v>11.39957155548989</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -569,12 +569,12 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>289.5485006821258</v>
+        <v>306.6128862407101</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>12.86724069769583</v>
+        <v>14.65789853853429</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -595,12 +595,12 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>217.721040797028</v>
+        <v>273.537576540357</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>9.201250578834143</v>
+        <v>12.02897500432825</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -621,12 +621,12 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>298.9230725109284</v>
+        <v>283.3855207317907</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>12.00235307737671</v>
+        <v>9.467449340451205</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -647,12 +647,12 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>620.5705802601036</v>
+        <v>478.3463936047028</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>24.50898429830133</v>
+        <v>25.58183359891947</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -673,12 +673,12 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>310.5351298771114</v>
+        <v>283.285195966335</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>10.53613642935987</v>
+        <v>9.448928033332697</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -699,12 +699,12 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>813.4528537523943</v>
+        <v>607.668628990844</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>25.63856825377426</v>
+        <v>20.56986107325004</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -725,12 +725,12 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>243.4865039945783</v>
+        <v>253.1276852898497</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>8.078937119136503</v>
+        <v>9.560021993429151</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -751,12 +751,12 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>171.831594423355</v>
+        <v>260.2252226410208</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>6.708681385557764</v>
+        <v>9.241803610273433</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -777,12 +777,12 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>260.614629597831</v>
+        <v>274.9416292117093</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>9.147753496969308</v>
+        <v>9.232519773872609</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -803,12 +803,12 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>181.2294101301109</v>
+        <v>259.2652523792486</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>6.00215753929527</v>
+        <v>9.541469478639298</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -829,12 +829,12 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>224.4681653878412</v>
+        <v>273.0455730596238</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>10.32400807911261</v>
+        <v>11.09081355499002</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -855,12 +855,12 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>119.8921695248892</v>
+        <v>262.5274822090996</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>3.618684123501609</v>
+        <v>8.898055568663199</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -881,12 +881,12 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>283.1115522992301</v>
+        <v>272.0576914914446</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>14.30054841045704</v>
+        <v>11.73644677622253</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -907,12 +907,12 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>147.4891082691907</v>
+        <v>268.7435706060456</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>5.701811343694116</v>
+        <v>9.164636847166159</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -933,12 +933,12 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>223.1330853050393</v>
+        <v>262.4191255282503</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>7.084764141270908</v>
+        <v>9.064975594554468</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -959,12 +959,12 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>204.682921829022</v>
+        <v>268.5440096646025</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>7.547390227858426</v>
+        <v>10.39999965048187</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -985,12 +985,12 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>146.0176258382641</v>
+        <v>263.2517743069592</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>4.745191002580068</v>
+        <v>10.02466766217647</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1011,12 +1011,12 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>206.3317690555035</v>
+        <v>274.3834393394563</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>8.810765928619837</v>
+        <v>10.87814843279565</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1037,12 +1037,12 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>219.9356143716117</v>
+        <v>260.8762415224003</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>8.904997046417753</v>
+        <v>8.999444834619569</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1063,12 +1063,12 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>324.8858149551142</v>
+        <v>283.7948394297751</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>12.29757140675225</v>
+        <v>9.543068203059841</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1089,12 +1089,12 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>897.3503321782962</v>
+        <v>614.9490655843009</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>20.10986367569337</v>
+        <v>18.09289749894094</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1115,12 +1115,12 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>327.8699504493716</v>
+        <v>283.285195966335</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>11.77031869105104</v>
+        <v>9.448928033332697</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1141,12 +1141,12 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>175.9936288449216</v>
+        <v>264.8274295493574</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>5.897597573930398</v>
+        <v>9.333673644822273</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1167,12 +1167,12 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>186.8977944487656</v>
+        <v>259.6288775002853</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>6.646747532657145</v>
+        <v>9.041563599512552</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1193,12 +1193,12 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>159.8358667878036</v>
+        <v>268.9137396317514</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>6.005338938476806</v>
+        <v>9.620377629807541</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1219,12 +1219,12 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>190.7199357722525</v>
+        <v>258.9983050693763</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>6.404152470348823</v>
+        <v>8.948105540316202</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1245,12 +1245,12 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>271.821000306116</v>
+        <v>258.8781217431748</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>12.18657463626084</v>
+        <v>9.466351722067666</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1271,12 +1271,12 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>265.8211763515511</v>
+        <v>283.7498872332715</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>10.74379049118423</v>
+        <v>9.534761612595945</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1297,12 +1297,12 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>973.4971391132553</v>
+        <v>614.9991470218339</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>25.7796215783605</v>
+        <v>18.37204655251781</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1323,12 +1323,12 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>652.8253975553612</v>
+        <v>469.4173384746964</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>24.20512501055465</v>
+        <v>23.7895181849088</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1349,12 +1349,12 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>178.0462564070317</v>
+        <v>260.0233552204824</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>5.002051537283394</v>
+        <v>10.11891037139517</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1375,12 +1375,12 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>210.4835487112126</v>
+        <v>274.4166281924735</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>11.62954266891588</v>
+        <v>11.52551769220261</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1401,12 +1401,12 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>836.9657162841271</v>
+        <v>611.3503717881184</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>25.55801144591133</v>
+        <v>19.57190394232211</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1427,12 +1427,12 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>314.3849130027971</v>
+        <v>283.285195966335</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>12.36220784399122</v>
+        <v>9.448928033332697</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -1453,12 +1453,12 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>941.3822368859518</v>
+        <v>615.0383023812344</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>29.16181180896738</v>
+        <v>18.21589763147882</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -1479,12 +1479,12 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>605.6533090260397</v>
+        <v>468.6744417152902</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>23.93689418370924</v>
+        <v>23.64765346086762</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1505,12 +1505,12 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>400.0698603080006</v>
+        <v>438.2041750319026</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>14.04336509926725</v>
+        <v>21.77729568565655</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1531,12 +1531,12 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>369.3261914635831</v>
+        <v>438.2041750319026</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>21.38215395923003</v>
+        <v>21.77729568565655</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1557,12 +1557,12 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>408.9187171577294</v>
+        <v>438.2041750319026</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>9.661157139776011</v>
+        <v>21.77729568565655</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1583,12 +1583,12 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>416.030095408967</v>
+        <v>438.20431856626</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>15.53112752357966</v>
+        <v>21.77730281883857</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -1609,12 +1609,12 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>445.0421429510677</v>
+        <v>438.204175747748</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>23.16235723016841</v>
+        <v>21.77729925224756</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -1635,12 +1635,12 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>519.1051742680455</v>
+        <v>473.6439615173157</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>16.80093378793335</v>
+        <v>29.16824950574167</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -1661,12 +1661,12 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>517.7394884356055</v>
+        <v>473.6439615173157</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>50.49074828756897</v>
+        <v>29.16824950574167</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1687,12 +1687,12 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>463.344199893606</v>
+        <v>473.6439615173157</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>20.2264858518564</v>
+        <v>29.16824950574167</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -1713,12 +1713,12 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>528.0177733738508</v>
+        <v>473.6439696363562</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>26.07672395943744</v>
+        <v>29.16824237255965</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>413.2245276675304</v>
+        <v>364.539623418353</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>21.63457587142056</v>
+        <v>14.74070675697272</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -1765,12 +1765,12 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>358.0023127067872</v>
+        <v>384.0401331314585</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>13.61056997989314</v>
+        <v>16.86699686157659</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -1791,12 +1791,12 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>477.1484229395755</v>
+        <v>468.4700792752442</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>20.89166744696251</v>
+        <v>25.03317598726761</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -1817,12 +1817,12 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>618.0666352710888</v>
+        <v>468.4700792752442</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>20.3305892935719</v>
+        <v>25.03317598726761</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -1843,12 +1843,12 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>467.7463813675583</v>
+        <v>468.4700792752442</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>21.55256924431178</v>
+        <v>25.03317598726761</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -1869,12 +1869,12 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>621.8777712385762</v>
+        <v>468.4699418869008</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>35.72453721443676</v>
+        <v>25.0331724206766</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -1895,12 +1895,12 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>392.4227631630488</v>
+        <v>410.2710263172093</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>41.37381407968098</v>
+        <v>20.69067131890737</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -1921,12 +1921,12 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>301.6057056798974</v>
+        <v>410.2710263172093</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>1.509591229103531</v>
+        <v>20.69067131890737</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -1947,12 +1947,12 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>415.892844833454</v>
+        <v>410.2710263172093</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>39.29695603483751</v>
+        <v>20.69067131890737</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -1973,12 +1973,12 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>530.3995707222064</v>
+        <v>463.0754773641796</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>7.17385580142242</v>
+        <v>28.05648602225365</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -1999,12 +1999,12 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>471.5072030269084</v>
+        <v>463.0755389518113</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>65.98825674812392</v>
+        <v>28.05648602225365</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -2025,12 +2025,12 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>445.732298841306</v>
+        <v>463.0755389518113</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>16.30911515392334</v>
+        <v>28.05648602225365</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -2051,12 +2051,12 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>157.8551200934199</v>
+        <v>273.6214855821115</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>6.685480711033231</v>
+        <v>11.1777902266722</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -2077,12 +2077,12 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>647.3257466924889</v>
+        <v>614.9490655843009</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>7.688863518536179</v>
+        <v>18.09289749894094</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -2103,12 +2103,12 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>329.4695477701716</v>
+        <v>438.2042460832471</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>14.4621613489244</v>
+        <v>21.77729568565655</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -2129,12 +2129,12 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>285.9194523508135</v>
+        <v>257.9986147447968</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>11.89370044882708</v>
+        <v>8.974888855510972</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -2155,12 +2155,12 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>295.3629391829428</v>
+        <v>270.4078102873163</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>15.34660815434614</v>
+        <v>10.82770791942698</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -2181,12 +2181,12 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>280.7546698520774</v>
+        <v>272.2541717319899</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>13.64687074319993</v>
+        <v>11.13280124766336</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>

--- a/data/output/20260922/pureComponents_filled.xlsx
+++ b/data/output/20260922/pureComponents_filled.xlsx
@@ -491,12 +491,12 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>258.7313393292955</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>9.382535050020962</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -517,12 +517,12 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-158.8591520830372</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>-0.7592581931408446</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -543,12 +543,12 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>250.0881919563437</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>11.39957155548989</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -569,12 +569,12 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>306.6128862407101</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>14.65789853853429</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -595,12 +595,12 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>273.537576540357</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>12.02897500432825</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -621,12 +621,12 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>283.3855207317907</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>9.467449340451205</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -647,12 +647,12 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>478.3463936047028</v>
+        <v>583.3011123372181</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>25.58183359891947</v>
+        <v>21.41850734383183</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -673,12 +673,12 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>283.285195966335</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>9.448928033332697</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -699,12 +699,12 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>607.668628990844</v>
+        <v>491.175757554105</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>20.56986107325004</v>
+        <v>67.86793680896861</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -725,12 +725,12 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>253.1276852898497</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>9.560021993429151</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -751,12 +751,12 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>260.2252226410208</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>9.241803610273433</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -777,12 +777,12 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>274.9416292117093</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>9.232519773872609</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -803,12 +803,12 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>259.2652523792486</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>9.541469478639298</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -829,12 +829,12 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>273.0455730596238</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>11.09081355499002</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -855,12 +855,12 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>262.5274822090996</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>8.898055568663199</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -881,12 +881,12 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>272.0576914914446</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>11.73644677622253</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -907,12 +907,12 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>268.7435706060456</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>9.164636847166159</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -933,12 +933,12 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>262.4191255282503</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>9.064975594554468</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -959,12 +959,12 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>268.5440096646025</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>10.39999965048187</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -985,12 +985,12 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>263.2517743069592</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>10.02466766217647</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1011,12 +1011,12 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>274.3834393394563</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>10.87814843279565</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1037,12 +1037,12 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>260.8762415224003</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>8.999444834619569</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1063,12 +1063,12 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>283.7948394297751</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>9.543068203059841</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1089,12 +1089,12 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>614.9490655843009</v>
+        <v>803.0617851852467</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>18.09289749894094</v>
+        <v>16.61415343709285</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1115,12 +1115,12 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>283.285195966335</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>9.448928033332697</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1141,12 +1141,12 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>264.8274295493574</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>9.333673644822273</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1167,12 +1167,12 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>259.6288775002853</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>9.041563599512552</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1193,12 +1193,12 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>268.9137396317514</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>9.620377629807541</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1219,12 +1219,12 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>258.9983050693763</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>8.948105540316202</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1245,12 +1245,12 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>258.8781217431748</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>9.466351722067666</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1271,12 +1271,12 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>283.7498872332715</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>9.534761612595945</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1297,12 +1297,12 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>614.9991470218339</v>
+        <v>666.8434992162204</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>18.37204655251781</v>
+        <v>24.89385972260391</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1323,12 +1323,12 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>469.4173384746964</v>
+        <v>565.1554905275908</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>23.7895181849088</v>
+        <v>23.48339252818729</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1349,12 +1349,12 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>260.0233552204824</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>10.11891037139517</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1375,12 +1375,12 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>274.4166281924735</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>11.52551769220261</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1401,12 +1401,12 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>611.3503717881184</v>
+        <v>559.7756311106002</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>19.57190394232211</v>
+        <v>40.91570440568245</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1427,12 +1427,12 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>283.285195966335</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>9.448928033332697</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -1453,12 +1453,12 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>615.0383023812344</v>
+        <v>696.074672609055</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>18.21589763147882</v>
+        <v>21.41935210891487</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -1479,12 +1479,12 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>468.6744417152902</v>
+        <v>643.4977038874974</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>23.64765346086762</v>
+        <v>16.63723315754158</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1505,12 +1505,12 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>438.2041750319026</v>
+        <v>456.3664772886538</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>21.77729568565655</v>
+        <v>15.34170502093584</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1531,12 +1531,12 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>438.2041750319026</v>
+        <v>428.7274566714589</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>21.77729568565655</v>
+        <v>23.45538266350177</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1557,12 +1557,12 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>438.2041750319026</v>
+        <v>510.0457399465345</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>21.77729568565655</v>
+        <v>10.25747252403096</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1583,12 +1583,12 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>438.20431856626</v>
+        <v>435.0814647870579</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>21.77730281883857</v>
+        <v>19.9505703776216</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -1609,12 +1609,12 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>438.204175747748</v>
+        <v>894.6713856931818</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>21.77729925224756</v>
+        <v>4.690976805757568</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -1635,12 +1635,12 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>473.6439615173157</v>
+        <v>718.062200641707</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>29.16824950574167</v>
+        <v>20.10121156871485</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -1661,12 +1661,12 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>473.6439615173157</v>
+        <v>468.8412421662727</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>29.16824950574167</v>
+        <v>47.95077394296876</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1687,12 +1687,12 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>473.6439615173157</v>
+        <v>889.2392477596832</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>29.16824950574167</v>
+        <v>16.54508381169491</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -1713,12 +1713,12 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>473.6439696363562</v>
+        <v>611.4738042241795</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>29.16824237255965</v>
+        <v>24.87009554326961</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>364.539623418353</v>
+        <v>364.2562288007246</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>14.74070675697272</v>
+        <v>-20.3035846553713</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -1765,12 +1765,12 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>384.0401331314585</v>
+        <v>405.830373283476</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>16.86699686157659</v>
+        <v>14.39315867720494</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -1791,12 +1791,12 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>468.4700792752442</v>
+        <v>614.6102646418841</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>25.03317598726761</v>
+        <v>17.82797641950539</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -1817,12 +1817,12 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>468.4700792752442</v>
+        <v>583.2841356369422</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>25.03317598726761</v>
+        <v>19.68787904070646</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -1843,12 +1843,12 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>468.4700792752442</v>
+        <v>621.3453346515953</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>25.03317598726761</v>
+        <v>17.4611856383866</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -1869,12 +1869,12 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>468.4699418869008</v>
+        <v>608.4244544167045</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>25.0331724206766</v>
+        <v>18.16938830068263</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -1895,12 +1895,12 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>410.2710263172093</v>
+        <v>397.7687891479598</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>20.69067131890737</v>
+        <v>41.47067668890788</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -1921,12 +1921,12 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>410.2710263172093</v>
+        <v>3071.281778975696</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>20.69067131890737</v>
+        <v>3.606906631131359</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -1947,12 +1947,12 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>410.2710263172093</v>
+        <v>399.4486669244831</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>20.69067131890737</v>
+        <v>38.60865922209713</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -1973,12 +1973,12 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>463.0754773641796</v>
+        <v>936.801012393846</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>28.05648602225365</v>
+        <v>9.929917413407912</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -1999,12 +1999,12 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>463.0755389518113</v>
+        <v>414.3240868625482</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>28.05648602225365</v>
+        <v>60.78523981463709</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -2025,12 +2025,12 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>463.0755389518113</v>
+        <v>-104.0806817565926</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>28.05648602225365</v>
+        <v>1.292844893860341</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -2051,12 +2051,12 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>273.6214855821115</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>11.1777902266722</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -2077,12 +2077,12 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>614.9490655843009</v>
+        <v>932.6856617145412</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>18.09289749894094</v>
+        <v>14.89188388772474</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -2103,12 +2103,12 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>438.2042460832471</v>
+        <v>817.9732365862526</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>21.77729568565655</v>
+        <v>7.657414814943262</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -2129,12 +2129,12 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>257.9986147447968</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>8.974888855510972</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -2155,12 +2155,12 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>270.4078102873163</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>10.82770791942698</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -2181,12 +2181,12 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>272.2541717319899</v>
+        <v>573.825988573062</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>11.13280124766336</v>
+        <v>18.71022352039648</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>

--- a/data/output/20260922/pureComponents_filled.xlsx
+++ b/data/output/20260922/pureComponents_filled.xlsx
@@ -491,12 +491,12 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>573.825988573062</v>
+        <v>192.9014862148218</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>18.71022352039648</v>
+        <v>5.141562176329536</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -517,12 +517,12 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>573.825988573062</v>
+        <v>258.6721566418234</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>18.71022352039648</v>
+        <v>7.299640955152869</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -543,12 +543,12 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>573.825988573062</v>
+        <v>301.4765309437644</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>18.71022352039648</v>
+        <v>17.84043170158235</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -569,12 +569,12 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>573.825988573062</v>
+        <v>179.6122284983203</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>18.71022352039648</v>
+        <v>3.642684331101819</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -595,12 +595,12 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>573.825988573062</v>
+        <v>257.3838342038833</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>18.71022352039648</v>
+        <v>10.51844297220097</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -621,12 +621,12 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>573.825988573062</v>
+        <v>379.8993081502928</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>18.71022352039648</v>
+        <v>21.9994947396767</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -647,12 +647,12 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>583.3011123372181</v>
+        <v>394.3210205162149</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>21.41850734383183</v>
+        <v>-30.09131551668166</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -673,12 +673,12 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>573.825988573062</v>
+        <v>198.5590420990659</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>18.71022352039648</v>
+        <v>4.329005840931938</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -699,12 +699,12 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>491.175757554105</v>
+        <v>439.149358471188</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>67.86793680896861</v>
+        <v>58.74639784914683</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -725,12 +725,12 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>573.825988573062</v>
+        <v>223.5655248200966</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>18.71022352039648</v>
+        <v>7.181705865833198</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -751,12 +751,12 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>573.825988573062</v>
+        <v>260.3192326026914</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>18.71022352039648</v>
+        <v>10.88229228404797</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -777,12 +777,12 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>573.825988573062</v>
+        <v>-195.7407799368402</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>18.71022352039648</v>
+        <v>-1.57858654073787</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -803,12 +803,12 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>573.825988573062</v>
+        <v>205.296649274973</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>18.71022352039648</v>
+        <v>5.881074938570688</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -829,12 +829,12 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>573.825988573062</v>
+        <v>241.0539203197087</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>18.71022352039648</v>
+        <v>8.728341270189429</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -855,12 +855,12 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>573.825988573062</v>
+        <v>138.4866163113635</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>18.71022352039648</v>
+        <v>2.811251897819734</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -881,12 +881,12 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>573.825988573062</v>
+        <v>289.1740859614783</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>18.71022352039648</v>
+        <v>15.34700977893356</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -907,12 +907,12 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>573.825988573062</v>
+        <v>158.1062048884453</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>18.71022352039648</v>
+        <v>3.514390227876763</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -933,12 +933,12 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>573.825988573062</v>
+        <v>149.0128382920888</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>18.71022352039648</v>
+        <v>3.172822742347932</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -959,12 +959,12 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>573.825988573062</v>
+        <v>307.3197516712137</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>18.71022352039648</v>
+        <v>19.1801999559184</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -985,12 +985,12 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>573.825988573062</v>
+        <v>249.4257299396556</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>18.71022352039648</v>
+        <v>9.598338190337977</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1011,12 +1011,12 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>573.825988573062</v>
+        <v>344.7504798856128</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>18.71022352039648</v>
+        <v>30.56612433138658</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1037,12 +1037,12 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>573.825988573062</v>
+        <v>158.2377428947362</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>18.71022352039648</v>
+        <v>3.520148100826308</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1063,12 +1063,12 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>573.825988573062</v>
+        <v>98.93866922394405</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>18.71022352039648</v>
+        <v>1.530454872003375</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1089,12 +1089,12 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>803.0617851852467</v>
+        <v>845.4796704454895</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>16.61415343709285</v>
+        <v>20.21709483741064</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1115,12 +1115,12 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>573.825988573062</v>
+        <v>248.6898958892509</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>18.71022352039648</v>
+        <v>6.701953113375204</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1141,12 +1141,12 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>573.825988573062</v>
+        <v>292.5692001776172</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>18.71022352039648</v>
+        <v>15.99364138271226</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1167,12 +1167,12 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>573.825988573062</v>
+        <v>219.733423854895</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>18.71022352039648</v>
+        <v>6.885519849827983</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1193,12 +1193,12 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>573.825988573062</v>
+        <v>335.108334808669</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>18.71022352039648</v>
+        <v>27.11455302473002</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1219,12 +1219,12 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>573.825988573062</v>
+        <v>153.707171388287</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>18.71022352039648</v>
+        <v>3.34605993577415</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1245,12 +1245,12 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>573.825988573062</v>
+        <v>208.0785089246558</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>18.71022352039648</v>
+        <v>6.061991137859554</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1271,12 +1271,12 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>573.825988573062</v>
+        <v>377.1783370318241</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>18.71022352039648</v>
+        <v>21.37501165253775</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1297,12 +1297,12 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>666.8434992162204</v>
+        <v>823.4780287621726</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>24.89385972260391</v>
+        <v>24.83055554156281</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1323,12 +1323,12 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>565.1554905275908</v>
+        <v>388.006629674968</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>23.48339252818729</v>
+        <v>-24.26190569266261</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1349,12 +1349,12 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>573.825988573062</v>
+        <v>230.5237071189078</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>18.71022352039648</v>
+        <v>7.757371593412293</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1375,12 +1375,12 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>573.825988573062</v>
+        <v>239.0830902754246</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>18.71022352039648</v>
+        <v>8.53623534659843</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1401,12 +1401,12 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>559.7756311106002</v>
+        <v>484.3989835468918</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>40.91570440568245</v>
+        <v>41.09974582606051</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1427,12 +1427,12 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>573.825988573062</v>
+        <v>306.3972162172316</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>18.71022352039648</v>
+        <v>11.01117580484944</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -1453,12 +1453,12 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>696.074672609055</v>
+        <v>818.8671271296046</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>21.41935210891487</v>
+        <v>27.41713514240423</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -1479,12 +1479,12 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>643.4977038874974</v>
+        <v>379.3704711677032</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>16.63723315754158</v>
+        <v>-18.66478901936607</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1505,12 +1505,12 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>456.3664772886538</v>
+        <v>420.9130736811304</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>15.34170502093584</v>
+        <v>14.02473433310737</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1531,12 +1531,12 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>428.7274566714589</v>
+        <v>375.1690432735642</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>23.45538266350177</v>
+        <v>21.46312888948713</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1557,12 +1557,12 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>510.0457399465345</v>
+        <v>419.3949897666078</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>10.25747252403096</v>
+        <v>10.32403832006198</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1583,12 +1583,12 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>435.0814647870579</v>
+        <v>427.3839743498265</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>19.9505703776216</v>
+        <v>122.3018878788312</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -1609,12 +1609,12 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>894.6713856931818</v>
+        <v>425.7093236555233</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>4.690976805757568</v>
+        <v>160.4245915363377</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -1635,12 +1635,12 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>718.062200641707</v>
+        <v>440.6777728780382</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>20.10121156871485</v>
+        <v>43.32695960273672</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -1661,12 +1661,12 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>468.8412421662727</v>
+        <v>490.4549247886379</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>47.95077394296876</v>
+        <v>49.6765488572357</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1687,12 +1687,12 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>889.2392477596832</v>
+        <v>441.653687139174</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>16.54508381169491</v>
+        <v>41.42323108550308</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -1713,12 +1713,12 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>611.4738042241795</v>
+        <v>428.2263154017148</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>24.87009554326961</v>
+        <v>109.3125685678461</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>364.2562288007246</v>
+        <v>458.5574927169193</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>-20.3035846553713</v>
+        <v>23.94916064390983</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -1765,12 +1765,12 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>405.830373283476</v>
+        <v>409.7444890643259</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>14.39315867720494</v>
+        <v>14.60339411778163</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -1791,12 +1791,12 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>614.6102646418841</v>
+        <v>532.0060881084693</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>17.82797641950539</v>
+        <v>9.502268651173141</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -1817,12 +1817,12 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>583.2841356369422</v>
+        <v>571.7285731550131</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>19.68787904070646</v>
+        <v>19.40236571542376</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -1843,12 +1843,12 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>621.3453346515953</v>
+        <v>569.8951815215686</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>17.4611856383866</v>
+        <v>7.598356861911826</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -1869,12 +1869,12 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>608.4244544167045</v>
+        <v>435.6658654185891</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>18.16938830068263</v>
+        <v>56.92899874562786</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -1895,12 +1895,12 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>397.7687891479598</v>
+        <v>409.4376446277737</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>41.47067668890788</v>
+        <v>41.46110484864718</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -1921,12 +1921,12 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3071.281778975696</v>
+        <v>344.2183178022885</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>3.606906631131359</v>
+        <v>2.811918676453047</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -1947,12 +1947,12 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>399.4486669244831</v>
+        <v>414.1348498664786</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>38.60865922209713</v>
+        <v>38.90161428099027</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -1973,12 +1973,12 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>936.801012393846</v>
+        <v>486.3275393629536</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>9.929917413407912</v>
+        <v>8.150951496199337</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -1999,12 +1999,12 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>414.3240868625482</v>
+        <v>469.4346553722007</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>60.78523981463709</v>
+        <v>64.1996855822201</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -2025,12 +2025,12 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-104.0806817565926</v>
+        <v>489.5133859042073</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>1.292844893860341</v>
+        <v>8.590057460009209</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -2051,12 +2051,12 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>573.825988573062</v>
+        <v>239.0830902754246</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>18.71022352039648</v>
+        <v>8.53623534659843</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -2077,12 +2077,12 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>932.6856617145412</v>
+        <v>668.1839542750452</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>14.89188388772474</v>
+        <v>7.924568177645284</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -2103,12 +2103,12 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>817.9732365862526</v>
+        <v>435.2796237019176</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>7.657414814943262</v>
+        <v>17.81036449794829</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -2129,12 +2129,12 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>573.825988573062</v>
+        <v>152.7973754649595</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>18.71022352039648</v>
+        <v>3.311737413527901</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -2155,12 +2155,12 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>573.825988573062</v>
+        <v>268.3492902425041</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>18.71022352039648</v>
+        <v>11.95500003933806</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -2181,12 +2181,12 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>573.825988573062</v>
+        <v>266.8357781986886</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>18.71022352039648</v>
+        <v>11.74547314250434</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>

--- a/data/output/20260922/pureComponents_filled.xlsx
+++ b/data/output/20260922/pureComponents_filled.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,27 +481,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ammonia borane</t>
+          <t>tetrabutylammonium bromide</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[BH3-][NH3+]</t>
+          <t>CCCC[N+](CCCC)(CCCC)CCCC.[Br-]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>176.3066398734335</v>
+        <v>420.7120932660865</v>
       </c>
       <c r="E2" t="n">
-        <v>32.32522033462445</v>
+        <v>24.16708557840721</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>3.973940692903351</v>
+        <v>14.10800338024954</v>
       </c>
       <c r="H2" t="n">
-        <v>4.686973258296501</v>
+        <v>3.747502429841876</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -511,27 +511,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tetramethylammonium borohydride</t>
+          <t>tetrabutylammonium chloride</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[BH4-].C[N+](C)(C)C</t>
+          <t>CCCC[N+](CCCC)(CCCC)CCCC.[Cl-]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>519.01506655898</v>
+        <v>375.1855292541242</v>
       </c>
       <c r="E3" t="n">
-        <v>61.40709247755789</v>
+        <v>18.79119442693167</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>10.50253330246275</v>
+        <v>21.4661139671739</v>
       </c>
       <c r="H3" t="n">
-        <v>7.151389675427904</v>
+        <v>3.901092812902125</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -541,33 +541,843 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tetrabutylammonium borohydride</t>
+          <t>tetrabutylammonium iodide</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[BH4-].CCCC[N+](CCCC)(CCCC)CCCC</t>
+          <t>CCCC[N+](CCCC)(CCCC)CCCC.[I-]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>436.3686975246674</v>
+        <v>420.2222438697347</v>
       </c>
       <c r="E4" t="n">
-        <v>34.44766431577133</v>
+        <v>28.32208795397853</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>17.67695535531796</v>
+        <v>10.253831318992</v>
       </c>
       <c r="H4" t="n">
-        <v>5.917310604525431</v>
+        <v>3.747389995547501</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tetraethylammonium chloride</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CC[N+](CC)(CC)CC.[Cl-]</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>490.4620894600857</v>
+      </c>
+      <c r="E5" t="n">
+        <v>15.09920206486957</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>49.68132498153454</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.901091868587166</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tetraethylammonium iodide</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CC[N+](CC)(CC)CC.[I-]</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>441.6909845911146</v>
+      </c>
+      <c r="E6" t="n">
+        <v>27.38658721533567</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>41.3823457669295</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7.151344859409485</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tetraheptylammonium chloride</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CCCCCCC[N+](CCCCCCC)(CCCCCCC)CCCCCCC.[Cl-]</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>458.5567158460356</v>
+      </c>
+      <c r="E7" t="n">
+        <v>37.01216295414262</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>23.94907084982593</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7.151391735927744</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tetrahexylammonium bromide</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CCCCCC[N+](CCCCCC)(CCCCCC)CCCCCC.[Br-]</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>409.6704680548245</v>
+      </c>
+      <c r="E8" t="n">
+        <v>24.28595017775668</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>14.60387762438727</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.900996019429761</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tetramethylammonium bromide</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C[N+](C)(C)C.[Br-]</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>532.1067248474651</v>
+      </c>
+      <c r="E9" t="n">
+        <v>65.81247331593046</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>9.505146666682949</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7.151389675427904</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tetramethylammonium chloride</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C[N+](C)(C)C.[Cl-]</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>571.7308634853503</v>
+      </c>
+      <c r="E10" t="n">
+        <v>27.3202265537058</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>19.40239334437265</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.901094819570653</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tetramethylammonium iodide</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C[N+](C)(C)C.[I-]</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>570.0174155880933</v>
+      </c>
+      <c r="E11" t="n">
+        <v>77.70714204161256</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>7.601082918202716</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7.151389932990416</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tetrapentylammonium bromide</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CCCCC[N+](CCCCC)(CCCCC)CCCCC.[Br-]</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>408.9880542888977</v>
+      </c>
+      <c r="E12" t="n">
+        <v>13.80538223912112</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>41.46392300143439</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.747520861371587</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tetrapentylammonium chloride</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CCCCC[N+](CCCCC)(CCCCC)CCCCC.[Cl-]</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>344.0087929441356</v>
+      </c>
+      <c r="E13" t="n">
+        <v>48.83665260037516</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>2.811846841185922</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.901093757216854</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tetrapentylammonium iodide</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CCCCC[N+](CCCCC)(CCCCC)CCCCC.[I-]</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>415.21765188174</v>
+      </c>
+      <c r="E14" t="n">
+        <v>14.41469956044916</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>38.8904706049363</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.747524056160851</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tetrapropylammonium bromide</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CCC[N+](CCC)(CCC)CCC.[Br-]</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>486.2777930373562</v>
+      </c>
+      <c r="E15" t="n">
+        <v>37.02816969922682</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>8.151146740771523</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.901091868587166</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tetrapropylammonium chloride</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CCC[N+](CCC)(CCC)CCC.[Cl-]</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>469.4500591428435</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12.83809759210431</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>64.19932824781439</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.901088091325045</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tetrapropylammonium iodide</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CCC[N+](CCC)(CCC)CCC.[I-]</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>485.2765046437429</v>
+      </c>
+      <c r="E17" t="n">
+        <v>48.0703247548059</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>9.315241849353852</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.527629083301898</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sodium borohydride</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[BH4-].[Na+]</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>627.0221072609049</v>
+      </c>
+      <c r="E18" t="n">
+        <v>31.71759522251416</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>15.32137886352693</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.739605025686855</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>potassium borohydride</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[BH4-].[K+]</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>711.7602040075116</v>
+      </c>
+      <c r="E19" t="n">
+        <v>34.11058467633628</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>17.53743284726232</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.854949705149991</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>lithium borohydride</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[BH4-].[Li+]</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>663.8131493051816</v>
+      </c>
+      <c r="E20" t="n">
+        <v>47.21581224053349</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>7.868726388070339</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.798360610145579</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>lithium chloride</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[Li+].[Cl-]</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>837.6643573271724</v>
+      </c>
+      <c r="E21" t="n">
+        <v>36.23155133888105</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>20.04615729349738</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.796347141984982</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>potassium chloride</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[K+].[Cl-]</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>818.922108906904</v>
+      </c>
+      <c r="E22" t="n">
+        <v>32.51279005118911</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>24.71983160790451</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.856757788451061</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sodium chloride</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[Na+].[Cl-]</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>816.5580631864398</v>
+      </c>
+      <c r="E23" t="n">
+        <v>29.7133914542151</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>27.54510598692723</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.7375670511527</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>butylamine borane</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CCCCN.[B]</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>265.6591458547038</v>
+      </c>
+      <c r="E24" t="n">
+        <v>18.13689885132972</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>11.37924313622762</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.466149506060634</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>hexylamine borane</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CCCCCCN.[B]</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>298.2974595700037</v>
+      </c>
+      <c r="E25" t="n">
+        <v>14.30454274584226</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>17.18160514024425</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.10454022745868</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>octylamine borane</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CCCCCCCCN.[B]</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>325.1484260374351</v>
+      </c>
+      <c r="E26" t="n">
+        <v>12.83518622090111</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>24.00815478143298</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.106807148380893</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>decylamine borane</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CCCCCCCCCCN.[B]</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>346.4251569356945</v>
+      </c>
+      <c r="E27" t="n">
+        <v>13.10707220238027</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>31.12765877257127</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.473133504145733</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>trimethylamine borane</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[B].CN(C)C</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>211.2069529206752</v>
+      </c>
+      <c r="E28" t="n">
+        <v>39.81474248034934</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>4.548552836564614</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.573624181747293</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>dimethylamine borane</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[B].CNC</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>211.2069529206752</v>
+      </c>
+      <c r="E29" t="n">
+        <v>39.81474248034934</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>4.548552836564614</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.573624181747293</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>dimethylamine</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CNC</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>217.4099906902875</v>
+      </c>
+      <c r="E30" t="n">
+        <v>26.34869976392622</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>6.345436524564708</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.272068500372467</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>trimethylamine</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CN(C)C</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>244.8979429919245</v>
+      </c>
+      <c r="E31" t="n">
+        <v>21.72152194311629</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>8.794378141906316</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.850918352817205</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/20260922/pureComponents_filled.xlsx
+++ b/data/output/20260922/pureComponents_filled.xlsx
@@ -491,21 +491,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>420.7120932660865</v>
+        <v>393.5195036242966</v>
       </c>
       <c r="E2" t="n">
-        <v>24.16708557840721</v>
+        <v>7.697212643460669</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>14.10800338024954</v>
+        <v>13.87355065866041</v>
       </c>
       <c r="H2" t="n">
-        <v>3.747502429841876</v>
+        <v>0.9641280380194192</v>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>-477.6987829880422</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11.42681654722231</v>
+      </c>
       <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -521,21 +525,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>375.1855292541242</v>
+        <v>328.8535726356333</v>
       </c>
       <c r="E3" t="n">
-        <v>18.79119442693167</v>
+        <v>5.472305180593917</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>21.4661139671739</v>
+        <v>19.98010717180457</v>
       </c>
       <c r="H3" t="n">
-        <v>3.901092812902125</v>
+        <v>0.96463539856848</v>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>-549.3558488950375</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11.42683670100018</v>
+      </c>
       <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -551,21 +559,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>420.2222438697347</v>
+        <v>419.3369202268792</v>
       </c>
       <c r="E4" t="n">
-        <v>28.32208795397853</v>
+        <v>9.786219915699908</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>10.253831318992</v>
+        <v>9.627238858489449</v>
       </c>
       <c r="H4" t="n">
-        <v>3.747389995547501</v>
+        <v>0.9633655256127373</v>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>-479.219347280542</v>
+      </c>
+      <c r="K4" t="n">
+        <v>11.42681996956445</v>
+      </c>
       <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -581,21 +593,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>490.4620894600857</v>
+        <v>531.0386917486145</v>
       </c>
       <c r="E5" t="n">
-        <v>15.09920206486957</v>
+        <v>5.281007358703983</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>49.68132498153454</v>
+        <v>51.23815822386265</v>
       </c>
       <c r="H5" t="n">
-        <v>3.901091868587166</v>
+        <v>0.9648887551740699</v>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>-396.2816647684566</v>
+      </c>
+      <c r="K5" t="n">
+        <v>11.42684012333629</v>
+      </c>
       <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -611,21 +627,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>441.6909845911146</v>
+        <v>532.8079145372034</v>
       </c>
       <c r="E6" t="n">
-        <v>27.38658721533567</v>
+        <v>36.99706331485863</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>41.3823457669295</v>
+        <v>15.41591094045456</v>
       </c>
       <c r="H6" t="n">
-        <v>7.151344859409485</v>
+        <v>5.042704718022685</v>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>-316.1893752964173</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11.42694545473527</v>
+      </c>
       <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -641,21 +661,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>458.5567158460356</v>
+        <v>516.6005501447406</v>
       </c>
       <c r="E7" t="n">
-        <v>37.01216295414262</v>
+        <v>78.30277237840936</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>23.94907084982593</v>
+        <v>10.99472940488357</v>
       </c>
       <c r="H7" t="n">
-        <v>7.151391735927744</v>
+        <v>9.245454745270553</v>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>-394.7369065992776</v>
+      </c>
+      <c r="K7" t="n">
+        <v>22.65356945521497</v>
+      </c>
       <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -671,21 +695,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>409.6704680548245</v>
+        <v>390.7612622134198</v>
       </c>
       <c r="E8" t="n">
-        <v>24.28595017775668</v>
+        <v>27.05605801909773</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>14.60387762438727</v>
+        <v>42.06031633280203</v>
       </c>
       <c r="H8" t="n">
-        <v>3.900996019429761</v>
+        <v>7.70483464160885</v>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>-400.6062811183883</v>
+      </c>
+      <c r="K8" t="n">
+        <v>21.741682595172</v>
+      </c>
       <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -701,21 +729,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>532.1067248474651</v>
+        <v>547.2571013901672</v>
       </c>
       <c r="E9" t="n">
-        <v>65.81247331593046</v>
+        <v>49.87315247038906</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>9.505146666682949</v>
+        <v>18.59231855904168</v>
       </c>
       <c r="H9" t="n">
-        <v>7.151389675427904</v>
+        <v>7.312517689482998</v>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>-256.7085111359928</v>
+      </c>
+      <c r="K9" t="n">
+        <v>11.42718995673099</v>
+      </c>
       <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -731,21 +763,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>571.7308634853503</v>
+        <v>639.8974479877101</v>
       </c>
       <c r="E10" t="n">
-        <v>27.3202265537058</v>
+        <v>9.965619886979079</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>19.40239334437265</v>
+        <v>20.49448489036292</v>
       </c>
       <c r="H10" t="n">
-        <v>3.901094819570653</v>
+        <v>0.96463539856848</v>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>-274.8530148511761</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.42683670100018</v>
+      </c>
       <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -761,21 +797,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>570.0174155880933</v>
+        <v>523.6370087785327</v>
       </c>
       <c r="E11" t="n">
-        <v>77.70714204161256</v>
+        <v>51.31501380558834</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>7.601082918202716</v>
+        <v>17.65538366913672</v>
       </c>
       <c r="H11" t="n">
-        <v>7.151389932990416</v>
+        <v>7.593646159675012</v>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>-199.2663254400912</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11.4269557216428</v>
+      </c>
       <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -791,21 +831,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>408.9880542888977</v>
+        <v>376.4028599151836</v>
       </c>
       <c r="E12" t="n">
-        <v>13.80538223912112</v>
+        <v>4.338743817931575</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>41.46392300143439</v>
+        <v>40.78097115490314</v>
       </c>
       <c r="H12" t="n">
-        <v>3.747520861371587</v>
+        <v>0.9790120208747308</v>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>-440.3427508592898</v>
+      </c>
+      <c r="K12" t="n">
+        <v>19.01940421366728</v>
+      </c>
       <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -821,21 +865,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>344.0087929441356</v>
+        <v>293.2642370568263</v>
       </c>
       <c r="E13" t="n">
-        <v>48.83665260037516</v>
+        <v>19.50129986517905</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>2.811846841185922</v>
+        <v>1.292538387279009</v>
       </c>
       <c r="H13" t="n">
-        <v>3.901093757216854</v>
+        <v>0.96463539856848</v>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>-502.0858804482</v>
+      </c>
+      <c r="K13" t="n">
+        <v>19.06352614778523</v>
+      </c>
       <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -851,21 +899,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>415.21765188174</v>
+        <v>411.7608376824052</v>
       </c>
       <c r="E14" t="n">
-        <v>14.41469956044916</v>
+        <v>4.789352389438414</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>38.8904706049363</v>
+        <v>39.31057560444692</v>
       </c>
       <c r="H14" t="n">
-        <v>3.747524056160851</v>
+        <v>0.9787694628898752</v>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>-447.2586191738933</v>
+      </c>
+      <c r="K14" t="n">
+        <v>19.01956322085327</v>
+      </c>
       <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -881,21 +933,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>486.2777930373562</v>
+        <v>582.8464217687481</v>
       </c>
       <c r="E15" t="n">
-        <v>37.02816969922682</v>
+        <v>15.3441610929291</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>8.151146740771523</v>
+        <v>7.2997386027138</v>
       </c>
       <c r="H15" t="n">
-        <v>3.901091868587166</v>
+        <v>0.9799804487914839</v>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>-441.8953477054676</v>
+      </c>
+      <c r="K15" t="n">
+        <v>11.42706447424515</v>
+      </c>
       <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -911,21 +967,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>469.4500591428435</v>
+        <v>473.7702307241585</v>
       </c>
       <c r="E16" t="n">
-        <v>12.83809759210431</v>
+        <v>4.164785642869529</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>64.19932824781439</v>
+        <v>66.5697075736968</v>
       </c>
       <c r="H16" t="n">
-        <v>3.901088091325045</v>
+        <v>0.9653949113002381</v>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>-487.513293248984</v>
+      </c>
+      <c r="K16" t="n">
+        <v>11.42684012333629</v>
+      </c>
       <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -941,21 +1001,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>485.2765046437429</v>
+        <v>648.2190965940993</v>
       </c>
       <c r="E17" t="n">
-        <v>48.0703247548059</v>
+        <v>70.77265705969319</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>9.315241849353852</v>
+        <v>5.149310703851018</v>
       </c>
       <c r="H17" t="n">
-        <v>5.527629083301898</v>
+        <v>4.748713098917997</v>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>-395.1112251517937</v>
+      </c>
+      <c r="K17" t="n">
+        <v>11.42682339190557</v>
+      </c>
       <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -971,21 +1035,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>627.0221072609049</v>
+        <v>674.599433092236</v>
       </c>
       <c r="E18" t="n">
-        <v>31.71759522251416</v>
+        <v>11.88249682551186</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>15.32137886352693</v>
+        <v>16.01117205112642</v>
       </c>
       <c r="H18" t="n">
-        <v>3.739605025686855</v>
+        <v>0.9716555302004191</v>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>-191.8982297710932</v>
+      </c>
+      <c r="K18" t="n">
+        <v>11.42693518781851</v>
+      </c>
       <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1001,21 +1069,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>711.7602040075116</v>
+        <v>875.9118265941776</v>
       </c>
       <c r="E19" t="n">
-        <v>34.11058467633628</v>
+        <v>13.98234702140033</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>17.53743284726232</v>
+        <v>19.18461153940743</v>
       </c>
       <c r="H19" t="n">
-        <v>3.854949705149991</v>
+        <v>0.9726460724430347</v>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>-226.8802116797079</v>
+      </c>
+      <c r="K19" t="n">
+        <v>11.42694203243071</v>
+      </c>
       <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1031,21 +1103,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>663.8131493051816</v>
+        <v>558.882261417661</v>
       </c>
       <c r="E20" t="n">
-        <v>47.21581224053349</v>
+        <v>14.90925257456579</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>7.868726388070339</v>
+        <v>7.139223883380172</v>
       </c>
       <c r="H20" t="n">
-        <v>3.798360610145579</v>
+        <v>0.9782838135969502</v>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>-190.4320669398047</v>
+      </c>
+      <c r="K20" t="n">
+        <v>11.42709831662703</v>
+      </c>
       <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1061,21 +1137,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>837.6643573271724</v>
+        <v>882.7779370999494</v>
       </c>
       <c r="E21" t="n">
-        <v>36.23155133888105</v>
+        <v>13.80584578564193</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>20.04615729349738</v>
+        <v>19.91317325562103</v>
       </c>
       <c r="H21" t="n">
-        <v>3.796347141984982</v>
+        <v>0.9648887551740699</v>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>-408.5581844172118</v>
+      </c>
+      <c r="K21" t="n">
+        <v>11.42683670100018</v>
+      </c>
       <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1091,21 +1171,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>818.922108906904</v>
+        <v>1047.279289869762</v>
       </c>
       <c r="E22" t="n">
-        <v>32.51279005118911</v>
+        <v>14.29134448959716</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>24.71983160790451</v>
+        <v>26.33588328927682</v>
       </c>
       <c r="H22" t="n">
-        <v>3.856757788451061</v>
+        <v>0.9934786754019052</v>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>-436.5922133155693</v>
+      </c>
+      <c r="K22" t="n">
+        <v>11.42732950684694</v>
+      </c>
       <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1121,21 +1205,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>816.5580631864398</v>
+        <v>1070.145192580918</v>
       </c>
       <c r="E23" t="n">
-        <v>29.7133914542151</v>
+        <v>13.50139194885515</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>27.54510598692723</v>
+        <v>30.35386218309965</v>
       </c>
       <c r="H23" t="n">
-        <v>3.7375670511527</v>
+        <v>0.9641280380194192</v>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>-411.0977767195561</v>
+      </c>
+      <c r="K23" t="n">
+        <v>11.42682339190557</v>
+      </c>
       <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1151,21 +1239,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>265.6591458547038</v>
+        <v>245.3907360079477</v>
       </c>
       <c r="E24" t="n">
-        <v>18.13689885132972</v>
+        <v>5.798872400555345</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>11.37924313622762</v>
+        <v>10.94438166599375</v>
       </c>
       <c r="H24" t="n">
-        <v>3.466149506060634</v>
+        <v>0.9699147602617423</v>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>-23.84049711942612</v>
+      </c>
+      <c r="K24" t="n">
+        <v>11.94127219387849</v>
+      </c>
       <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1181,21 +1273,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>298.2974595700037</v>
+        <v>279.465336423037</v>
       </c>
       <c r="E25" t="n">
-        <v>14.30454274584226</v>
+        <v>5.387579812686496</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>17.18160514024425</v>
+        <v>15.33108722647065</v>
       </c>
       <c r="H25" t="n">
-        <v>3.10454022745868</v>
+        <v>0.9453053299347222</v>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>-29.02612087697651</v>
+      </c>
+      <c r="K25" t="n">
+        <v>12.93393869209021</v>
+      </c>
       <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1211,21 +1307,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>325.1484260374351</v>
+        <v>307.767125472662</v>
       </c>
       <c r="E26" t="n">
-        <v>12.83518622090111</v>
+        <v>4.727966260979756</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>24.00815478143298</v>
+        <v>23.60231617822987</v>
       </c>
       <c r="H26" t="n">
-        <v>3.106807148380893</v>
+        <v>0.9514401569656239</v>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>-40.99214809651687</v>
+      </c>
+      <c r="K26" t="n">
+        <v>14.81364549373433</v>
+      </c>
       <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1241,21 +1341,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>346.4251569356945</v>
+        <v>323.4595867050642</v>
       </c>
       <c r="E27" t="n">
-        <v>13.10707220238027</v>
+        <v>4.394402532090263</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>31.12765877257127</v>
+        <v>30.71074486824374</v>
       </c>
       <c r="H27" t="n">
-        <v>3.473133504145733</v>
+        <v>0.9871537645846763</v>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>-53.2246903340166</v>
+      </c>
+      <c r="K27" t="n">
+        <v>16.11022748759359</v>
+      </c>
       <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1271,21 +1375,25 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>211.2069529206752</v>
+        <v>384.485681317903</v>
       </c>
       <c r="E28" t="n">
-        <v>39.81474248034934</v>
+        <v>65.69847339846032</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>4.548552836564614</v>
+        <v>6.870457106380872</v>
       </c>
       <c r="H28" t="n">
-        <v>5.573624181747293</v>
+        <v>7.649343374412345</v>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>-137.9764312837704</v>
+      </c>
+      <c r="K28" t="n">
+        <v>18.34818092002206</v>
+      </c>
       <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1301,21 +1409,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>211.2069529206752</v>
+        <v>384.485681317903</v>
       </c>
       <c r="E29" t="n">
-        <v>39.81474248034934</v>
+        <v>65.69847339846032</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>4.548552836564614</v>
+        <v>6.870457106380872</v>
       </c>
       <c r="H29" t="n">
-        <v>5.573624181747293</v>
+        <v>7.649343374412345</v>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>-137.9764312837704</v>
+      </c>
+      <c r="K29" t="n">
+        <v>18.34818092002206</v>
+      </c>
       <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1331,21 +1443,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>217.4099906902875</v>
+        <v>177.6050333866868</v>
       </c>
       <c r="E30" t="n">
-        <v>26.34869976392622</v>
+        <v>6.110096585366507</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>6.345436524564708</v>
+        <v>5.907841076621981</v>
       </c>
       <c r="H30" t="n">
-        <v>4.272068500372467</v>
+        <v>0.955899462600454</v>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>-21.46831532008065</v>
+      </c>
+      <c r="K30" t="n">
+        <v>11.42681996956445</v>
+      </c>
       <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1361,21 +1477,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>244.8979429919245</v>
+        <v>154.2699185191374</v>
       </c>
       <c r="E31" t="n">
-        <v>21.72152194311629</v>
+        <v>5.268738709242995</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>8.794378141906316</v>
+        <v>6.572760265256468</v>
       </c>
       <c r="H31" t="n">
-        <v>3.850918352817205</v>
+        <v>0.9633655256127373</v>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>-27.18008637277029</v>
+      </c>
+      <c r="K31" t="n">
+        <v>11.42680970253494</v>
+      </c>
       <c r="L31" t="inlineStr"/>
     </row>
   </sheetData>
